--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0001T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>14.72169265787015</v>
+        <v>2.3922750569039</v>
       </c>
       <c r="D2" t="n">
-        <v>14.49940273029319</v>
+        <v>2.356152943672644</v>
       </c>
       <c r="E2" t="n">
-        <v>13.08885573973749</v>
+        <v>2.126939057707342</v>
       </c>
       <c r="F2" t="n">
-        <v>16.03603204999351</v>
+        <v>2.605855208123945</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>33.19877067052725</v>
+        <v>5.394800233960678</v>
       </c>
       <c r="D3" t="n">
-        <v>33.17483693494307</v>
+        <v>5.39091100192825</v>
       </c>
       <c r="E3" t="n">
-        <v>13.08885573973749</v>
+        <v>2.126939057707342</v>
       </c>
       <c r="F3" t="n">
-        <v>16.03603204999351</v>
+        <v>2.605855208123945</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>36.32992701691857</v>
+        <v>5.903613140249267</v>
       </c>
       <c r="D4" t="n">
-        <v>36.42304338161436</v>
+        <v>5.918744549512335</v>
       </c>
       <c r="E4" t="n">
-        <v>13.08885573973749</v>
+        <v>2.126939057707342</v>
       </c>
       <c r="F4" t="n">
-        <v>16.03603204999351</v>
+        <v>2.605855208123945</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>53.03294071335331</v>
+        <v>8.617852865919913</v>
       </c>
       <c r="D5" t="n">
-        <v>52.96475998422614</v>
+        <v>8.606773497436748</v>
       </c>
       <c r="E5" t="n">
-        <v>13.08885573973749</v>
+        <v>2.126939057707342</v>
       </c>
       <c r="F5" t="n">
-        <v>16.03603204999351</v>
+        <v>2.605855208123945</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>22.02851453238301</v>
+        <v>3.579633611512238</v>
       </c>
       <c r="D6" t="n">
-        <v>22.35172957124255</v>
+        <v>3.632156055326915</v>
       </c>
       <c r="E6" t="n">
-        <v>13.08885573973749</v>
+        <v>2.126939057707342</v>
       </c>
       <c r="F6" t="n">
-        <v>16.03603204999351</v>
+        <v>2.605855208123945</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>38.73413025518526</v>
+        <v>6.294296166467604</v>
       </c>
       <c r="D7" t="n">
-        <v>38.21052016164951</v>
+        <v>6.209209526268046</v>
       </c>
       <c r="E7" t="n">
-        <v>13.08885573973749</v>
+        <v>2.126939057707342</v>
       </c>
       <c r="F7" t="n">
-        <v>16.03603204999351</v>
+        <v>2.605855208123945</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>64.72939264726108</v>
+        <v>10.51852630517993</v>
       </c>
       <c r="D8" t="n">
-        <v>64.19493985261319</v>
+        <v>10.43167772604964</v>
       </c>
       <c r="E8" t="n">
-        <v>13.08885573973749</v>
+        <v>2.126939057707342</v>
       </c>
       <c r="F8" t="n">
-        <v>16.03603204999351</v>
+        <v>2.605855208123945</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>32.45430733223797</v>
+        <v>5.273824941488671</v>
       </c>
       <c r="D9" t="n">
-        <v>31.57125622847626</v>
+        <v>5.130329137127393</v>
       </c>
       <c r="E9" t="n">
-        <v>13.08885573973749</v>
+        <v>2.126939057707342</v>
       </c>
       <c r="F9" t="n">
-        <v>16.03603204999351</v>
+        <v>2.605855208123945</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.74173397047632</v>
+        <v>6.458031770202401</v>
       </c>
       <c r="D10" t="n">
-        <v>7.732040463497223</v>
+        <v>1.256456575318299</v>
       </c>
       <c r="E10" t="n">
-        <v>13.08885573973749</v>
+        <v>2.126939057707342</v>
       </c>
       <c r="F10" t="n">
-        <v>16.03603204999351</v>
+        <v>2.605855208123945</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.14624289315112</v>
+        <v>4.411264470137057</v>
       </c>
       <c r="D11" t="n">
-        <v>14.57538526719098</v>
+        <v>2.368500105918535</v>
       </c>
       <c r="E11" t="n">
-        <v>13.08885573973749</v>
+        <v>2.126939057707342</v>
       </c>
       <c r="F11" t="n">
-        <v>16.03603204999351</v>
+        <v>2.605855208123945</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>37.30547957397494</v>
+        <v>6.062140430770927</v>
       </c>
       <c r="D12" t="n">
-        <v>29.78249642671546</v>
+        <v>4.839655669341262</v>
       </c>
       <c r="E12" t="n">
-        <v>13.08885573973749</v>
+        <v>2.126939057707342</v>
       </c>
       <c r="F12" t="n">
-        <v>16.03603204999351</v>
+        <v>2.605855208123945</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
